--- a/dados/imoveis_importacao.xlsx
+++ b/dados/imoveis_importacao.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desktop\Desktop\SENAI\03 - PWBE\02 - PWBE 2DS\17 - Aluguel\Sistema_aluguel_apostila\front\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\43283927863\Documents\superlogica\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495BA6E2-DAB5-4D7D-B9D3-F3EB55BE73F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E5FF4A-F8BD-4409-87BA-4E3D02D105A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="imoveis" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -468,6 +463,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
